--- a/examples/sequence/OUL/result/animal_id_indexed_result_data-10-cut-5.xlsx
+++ b/examples/sequence/OUL/result/animal_id_indexed_result_data-10-cut-5.xlsx
@@ -457,25 +457,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>SecondsObserving</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
       <c r="F1" s="1" t="n"/>
       <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="n"/>
       <c r="K1" s="1" t="n"/>
       <c r="L1" s="1" t="n"/>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>ObjectsInUpdatingLocationsTrainingTrial</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="N1" s="1" t="n"/>
@@ -507,7 +519,7 @@
       <c r="AN1" s="1" t="n"/>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>ObjectsInUpdatingLocationsUpdateTrial</t>
+          <t>Update</t>
         </is>
       </c>
       <c r="AP1" s="1" t="n"/>
@@ -539,7 +551,7 @@
       <c r="BP1" s="1" t="n"/>
       <c r="BQ1" s="1" t="inlineStr">
         <is>
-          <t>ObjectsInUpdatingLocationsTestTrial</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="BR1" s="1" t="n"/>
@@ -571,62 +583,34 @@
       <c r="CR1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>object_1</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>object_2</t>
-        </is>
-      </c>
+          <t>SecondsObserving</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>object_1</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>object_4</t>
-        </is>
-      </c>
+          <t>SecondsObserving</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>object_1</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>object_2</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>object_3</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>object_4</t>
-        </is>
-      </c>
+          <t>SecondsObserving</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
       <c r="M2" s="1" t="inlineStr">
         <is>
           <t>All</t>
@@ -773,18 +757,66 @@
       <c r="CR2" s="1" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr"/>
-      <c r="B3" s="1" t="inlineStr"/>
-      <c r="C3" s="1" t="inlineStr"/>
-      <c r="D3" s="1" t="inlineStr"/>
-      <c r="E3" s="1" t="inlineStr"/>
-      <c r="F3" s="1" t="inlineStr"/>
-      <c r="G3" s="1" t="inlineStr"/>
-      <c r="H3" s="1" t="inlineStr"/>
-      <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr"/>
-      <c r="K3" s="1" t="inlineStr"/>
-      <c r="L3" s="1" t="inlineStr"/>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Location/Category</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>object_1</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>object_2</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>object_1</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>object_4</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>object_1</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>object_2</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>object_3</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>object_4</t>
+        </is>
+      </c>
       <c r="M3" s="1" t="inlineStr">
         <is>
           <t>Displacement</t>
@@ -1220,46 +1252,46 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35.16666666666666</v>
+        <v>43.83333333333334</v>
       </c>
       <c r="C5" t="n">
-        <v>7.866666666666666</v>
+        <v>12.23333333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>17.03333333333333</v>
+        <v>31.6</v>
       </c>
       <c r="E5" t="n">
-        <v>4.766666666666667</v>
+        <v>5.266666666666667</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2666666666666667</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>3.066666666666667</v>
+        <v>5.266666666666667</v>
       </c>
       <c r="H5" t="n">
-        <v>33.06666666666667</v>
+        <v>11.26666666666667</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="L5" t="n">
-        <v>9.1</v>
+        <v>4.133333333333334</v>
       </c>
       <c r="M5" t="n">
-        <v>44.2723054251108</v>
+        <v>43.95105330914401</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03033226224882007</v>
+        <v>0.03005771088053455</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01372990293518817</v>
+        <v>0.01362321097832764</v>
       </c>
       <c r="P5" t="n">
         <v>5.3</v>
@@ -1301,22 +1333,22 @@
         <v>177.5333333333333</v>
       </c>
       <c r="AC5" t="n">
-        <v>26.8064529719244</v>
+        <v>26.18138026537319</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.02773337996760144</v>
+        <v>0.0275005987000965</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.01319237562507357</v>
+        <v>0.01279030729741634</v>
       </c>
       <c r="AF5" t="n">
         <v>5.300000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AH5" t="n">
-        <v>156.9666666666667</v>
+        <v>153.2666666666667</v>
       </c>
       <c r="AI5" t="n">
         <v>23.41219775504355</v>
@@ -1331,31 +1363,31 @@
         <v>2.1</v>
       </c>
       <c r="AM5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AN5" t="n">
-        <v>516.6</v>
+        <v>512.8</v>
       </c>
       <c r="AO5" t="n">
-        <v>12.59178013102488</v>
+        <v>12.16831227896911</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.01901920678563085</v>
+        <v>0.0191224405811749</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.01126341575546491</v>
+        <v>0.01099945006125491</v>
       </c>
       <c r="AR5" t="n">
         <v>6.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.90443816274852</v>
+        <v>2.301779274444138</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.04372772001657022</v>
+        <v>0.0432008025689222</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.03068762173958555</v>
+        <v>0.02450240725358651</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -1364,7 +1396,7 @@
         <v>4</v>
       </c>
       <c r="AX5" t="n">
-        <v>53.7</v>
+        <v>53.56666666666667</v>
       </c>
       <c r="AY5" t="n">
         <v>4.983309141187457</v>
@@ -1382,7 +1414,7 @@
         <v>7</v>
       </c>
       <c r="BD5" t="n">
-        <v>215.9</v>
+        <v>203.8666666666667</v>
       </c>
       <c r="BE5" t="n">
         <v>0.5237467580143156</v>
@@ -1421,88 +1453,88 @@
         <v>21.23333333333333</v>
       </c>
       <c r="BQ5" t="n">
-        <v>29.85723740120597</v>
+        <v>11.31675354819877</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.02755373319848531</v>
+        <v>0.01532047688854243</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.01335860775034492</v>
+        <v>0.006141066784671412</v>
       </c>
       <c r="BT5" t="n">
-        <v>7.366666666666666</v>
+        <v>5.266666666666667</v>
       </c>
       <c r="BU5" t="n">
-        <v>6.468811500028487</v>
+        <v>2.624197459572537</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.05788317321888764</v>
+        <v>0.04768281327438562</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.02953654019141835</v>
+        <v>0.01892981337136149</v>
       </c>
       <c r="BX5" t="n">
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BZ5" t="n">
-        <v>98.83333333333333</v>
+        <v>33.93333333333333</v>
       </c>
       <c r="CA5" t="n">
-        <v>10.65728733878331</v>
+        <v>3.920405092565982</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.02931598039667598</v>
+        <v>0.02099303068242192</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.01819068255005062</v>
+        <v>0.01150398587239309</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.133333333333334</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="CE5" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="CF5" t="n">
-        <v>203.2333333333333</v>
+        <v>122.2666666666667</v>
       </c>
       <c r="CG5" t="n">
-        <v>9.953309789509577</v>
+        <v>0.6250637516124264</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.04133209288651037</v>
+        <v>0.01196176349566502</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.02179707975691132</v>
+        <v>0.004231315601880503</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="CL5" t="n">
-        <v>114.7333333333333</v>
+        <v>41.46666666666667</v>
       </c>
       <c r="CM5" t="n">
-        <v>7.944614110711182</v>
+        <v>2.326875952961025</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.02933273093590311</v>
+        <v>0.01770541361382079</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.0161847500139825</v>
+        <v>0.008308678108150596</v>
       </c>
       <c r="CP5" t="n">
         <v>4.233333333333333</v>
       </c>
       <c r="CQ5" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="CR5" t="n">
-        <v>188.3333333333333</v>
+        <v>102.3333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -1512,43 +1544,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.2</v>
+        <v>44.36666666666667</v>
       </c>
       <c r="C6" t="n">
-        <v>7.133333333333334</v>
+        <v>13.8</v>
       </c>
       <c r="D6" t="n">
-        <v>17.93333333333333</v>
+        <v>30.56666666666667</v>
       </c>
       <c r="E6" t="n">
-        <v>9.033333333333333</v>
+        <v>11.63333333333333</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7666666666666667</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>8.233333333333333</v>
+        <v>11.63333333333333</v>
       </c>
       <c r="H6" t="n">
-        <v>18.1</v>
+        <v>6.4</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7666666666666667</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>4.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="L6" t="n">
-        <v>6.066666666666666</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>53.88220391786516</v>
+        <v>53.69832763787824</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03751990039463859</v>
+        <v>0.03738060413530281</v>
       </c>
       <c r="O6" t="n">
         <v>0.0186184532169984</v>
@@ -1605,10 +1637,10 @@
         <v>2.2</v>
       </c>
       <c r="AG6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AH6" t="n">
-        <v>235.4333333333333</v>
+        <v>231.6666666666667</v>
       </c>
       <c r="AI6" t="n">
         <v>34.62761596357814</v>
@@ -1629,13 +1661,13 @@
         <v>528.6333333333333</v>
       </c>
       <c r="AO6" t="n">
-        <v>28.83040937352069</v>
+        <v>26.85052743625271</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.03171542293586793</v>
+        <v>0.03107465168626172</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.01449657764165302</v>
+        <v>0.01354487377707281</v>
       </c>
       <c r="AR6" t="n">
         <v>2.133333333333333</v>
@@ -1677,124 +1709,124 @@
         <v>68.23333333333333</v>
       </c>
       <c r="BE6" t="n">
-        <v>14.47403222516276</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.02991396827079652</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.01507931262801281</v>
+        <v>0</v>
       </c>
       <c r="BH6" t="n">
-        <v>1.066666666666667</v>
+        <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>35</v>
+        <v>21.93333333333333</v>
       </c>
       <c r="BK6" t="n">
-        <v>17.75739013063103</v>
+        <v>16.92500107034165</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.02876455684563717</v>
+        <v>0.02793767987202933</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.02526099767625685</v>
+        <v>0.02557984122032087</v>
       </c>
       <c r="BN6" t="n">
         <v>2.133333333333333</v>
       </c>
       <c r="BO6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BP6" t="n">
-        <v>211.3</v>
+        <v>198.4666666666667</v>
       </c>
       <c r="BQ6" t="n">
-        <v>36.4526630457058</v>
+        <v>11.91243303219392</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.03072283414517718</v>
+        <v>0.02269101965989467</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.01396001999024937</v>
+        <v>0.006802553067611239</v>
       </c>
       <c r="BT6" t="n">
         <v>1.033333333333333</v>
       </c>
       <c r="BU6" t="n">
-        <v>19.80080217328126</v>
+        <v>0.9346487079162578</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.04246544253709006</v>
+        <v>0.05816377418901279</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.02109298138862485</v>
+        <v>0.01884795557264885</v>
       </c>
       <c r="BX6" t="n">
         <v>0</v>
       </c>
       <c r="BY6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.451530201228303</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0.06858859525186976</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.03603610013591595</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>3.113729229142395</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.04076867092189199</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.02303622693780163</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="n">
         <v>6</v>
       </c>
-      <c r="BZ6" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>10.13996166760537</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>0.06550898636553629</v>
-      </c>
-      <c r="CC6" t="n">
-        <v>0.06190426671666885</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>9</v>
-      </c>
-      <c r="CF6" t="n">
-        <v>58.83333333333334</v>
-      </c>
-      <c r="CG6" t="n">
-        <v>8.155317645355062</v>
-      </c>
-      <c r="CH6" t="n">
-        <v>0.04173127712968799</v>
-      </c>
-      <c r="CI6" t="n">
-        <v>0.02581029187852141</v>
-      </c>
-      <c r="CJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK6" t="n">
-        <v>15</v>
-      </c>
       <c r="CL6" t="n">
-        <v>154.1333333333333</v>
+        <v>60.3</v>
       </c>
       <c r="CM6" t="n">
-        <v>20.16460100491749</v>
+        <v>5.033158995236779</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0315215909571498</v>
+        <v>0.02128600335163264</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.01956077222814855</v>
+        <v>0.00801551171761763</v>
       </c>
       <c r="CP6" t="n">
         <v>1.033333333333333</v>
       </c>
       <c r="CQ6" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="CR6" t="n">
-        <v>359.4666666666666</v>
+        <v>206.7</v>
       </c>
     </row>
     <row r="7">
@@ -1804,43 +1836,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>66.06666666666666</v>
+        <v>78.66666666666667</v>
       </c>
       <c r="C7" t="n">
-        <v>15.03333333333333</v>
+        <v>24.93333333333333</v>
       </c>
       <c r="D7" t="n">
-        <v>32.86666666666667</v>
+        <v>53.76666666666667</v>
       </c>
       <c r="E7" t="n">
-        <v>8.233333333333333</v>
+        <v>9.933333333333334</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>5.966666666666667</v>
+        <v>9.933333333333334</v>
       </c>
       <c r="H7" t="n">
-        <v>24.46666666666667</v>
+        <v>9.966666666666667</v>
       </c>
       <c r="I7" t="n">
-        <v>7.766666666666667</v>
+        <v>5.233333333333333</v>
       </c>
       <c r="J7" t="n">
-        <v>4.533333333333333</v>
+        <v>4.733333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>2.966666666666667</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>7.366666666666666</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>83.98819213893667</v>
+        <v>83.43765368057896</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05459236445243354</v>
+        <v>0.05519172968566333</v>
       </c>
       <c r="O7" t="n">
         <v>0.03105495653379597</v>
@@ -1861,28 +1893,28 @@
         <v>1.066666666666667</v>
       </c>
       <c r="U7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="V7" t="n">
-        <v>145.0333333333333</v>
+        <v>139.7</v>
       </c>
       <c r="W7" t="n">
-        <v>48.27957997786003</v>
+        <v>46.96033038079435</v>
       </c>
       <c r="X7" t="n">
-        <v>0.06362644096383398</v>
+        <v>0.06266289833242993</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.04453565528928465</v>
+        <v>0.04430272206333943</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AB7" t="n">
-        <v>177.7333333333333</v>
+        <v>175.7666666666667</v>
       </c>
       <c r="AC7" t="n">
         <v>38.8609005442744</v>
@@ -1921,13 +1953,13 @@
         <v>418.1666666666667</v>
       </c>
       <c r="AO7" t="n">
-        <v>23.57207030553625</v>
+        <v>21.59168794431417</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.03597636232761153</v>
+        <v>0.03583651392598625</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.02213558395288928</v>
+        <v>0.02166636467970628</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -1969,124 +2001,124 @@
         <v>47.53333333333333</v>
       </c>
       <c r="BE7" t="n">
-        <v>12.39207910981448</v>
+        <v>10.15607586434507</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.03854311311522943</v>
+        <v>0.04058492011459858</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.02403001597687375</v>
+        <v>0.02686996304877687</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BJ7" t="n">
-        <v>108.5666666666667</v>
+        <v>92.56666666666666</v>
       </c>
       <c r="BK7" t="n">
-        <v>10.51847037858425</v>
+        <v>8.600638860765436</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.04456476488045465</v>
+        <v>0.05299900658134432</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.03287503234446034</v>
+        <v>0.03943690461455251</v>
       </c>
       <c r="BN7" t="n">
         <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BP7" t="n">
-        <v>94.63333333333334</v>
+        <v>84.63333333333334</v>
       </c>
       <c r="BQ7" t="n">
-        <v>45.54293992671805</v>
+        <v>21.53154457268311</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.038394833679539</v>
+        <v>0.02395903389772519</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.02022788386971119</v>
+        <v>0.01276290396730406</v>
       </c>
       <c r="BT7" t="n">
         <v>0</v>
       </c>
       <c r="BU7" t="n">
-        <v>20.29933159243857</v>
+        <v>9.497312122953128</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.0403579251259404</v>
+        <v>0.02962265176577557</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.0264659737060192</v>
+        <v>0.02422281113978508</v>
       </c>
       <c r="BX7" t="n">
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BZ7" t="n">
-        <v>169.4666666666667</v>
+        <v>123.4</v>
       </c>
       <c r="CA7" t="n">
-        <v>25.73960332707558</v>
+        <v>10.58304013634073</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.04083240433263961</v>
+        <v>0.04289418080041865</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.02592244310740988</v>
+        <v>0.02380670793299068</v>
       </c>
       <c r="CD7" t="n">
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="CF7" t="n">
-        <v>125</v>
+        <v>53.8</v>
       </c>
       <c r="CG7" t="n">
-        <v>17.02999590252613</v>
+        <v>3.595502687164976</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0563361727883614</v>
+        <v>0.04557783429750072</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.02998401630327523</v>
+        <v>0.02968464585331664</v>
       </c>
       <c r="CJ7" t="n">
         <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="CL7" t="n">
-        <v>138.1</v>
+        <v>63.4</v>
       </c>
       <c r="CM7" t="n">
-        <v>19.10873541854633</v>
+        <v>8.443566508114252</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0432785386486685</v>
+        <v>0.04531152452646145</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.02510482360300586</v>
+        <v>0.0213637777691742</v>
       </c>
       <c r="CP7" t="n">
         <v>0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="CR7" t="n">
-        <v>176.2666666666667</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="8">
@@ -2096,58 +2128,58 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>75.46666666666667</v>
+        <v>99.8</v>
       </c>
       <c r="C8" t="n">
-        <v>32.03333333333333</v>
+        <v>49.5</v>
       </c>
       <c r="D8" t="n">
-        <v>37.56666666666667</v>
+        <v>50.3</v>
       </c>
       <c r="E8" t="n">
-        <v>12.83333333333333</v>
+        <v>23.9</v>
       </c>
       <c r="F8" t="n">
-        <v>5.8</v>
+        <v>8.466666666666667</v>
       </c>
       <c r="G8" t="n">
-        <v>8.466666666666667</v>
+        <v>15.43333333333333</v>
       </c>
       <c r="H8" t="n">
-        <v>17.1</v>
+        <v>17.4</v>
       </c>
       <c r="I8" t="n">
-        <v>2.866666666666667</v>
+        <v>2.366666666666667</v>
       </c>
       <c r="J8" t="n">
-        <v>6.566666666666666</v>
+        <v>5.2</v>
       </c>
       <c r="K8" t="n">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="L8" t="n">
-        <v>5.833333333333333</v>
+        <v>6.033333333333333</v>
       </c>
       <c r="M8" t="n">
-        <v>85.45705517406154</v>
+        <v>84.98782569770731</v>
       </c>
       <c r="N8" t="n">
-        <v>0.06523777568434819</v>
+        <v>0.06512113165996469</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03741011335984928</v>
+        <v>0.03744144770546065</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>42.1783486431159</v>
+        <v>40.53436497771108</v>
       </c>
       <c r="R8" t="n">
-        <v>0.06865115730596523</v>
+        <v>0.067518765647457</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03870066451990467</v>
+        <v>0.03749325515026465</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -2156,7 +2188,7 @@
         <v>41</v>
       </c>
       <c r="V8" t="n">
-        <v>158.5666666666667</v>
+        <v>158.5333333333333</v>
       </c>
       <c r="W8" t="n">
         <v>45.49980969612118</v>
@@ -2171,10 +2203,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AB8" t="n">
-        <v>248.4666666666667</v>
+        <v>242.2666666666667</v>
       </c>
       <c r="AC8" t="n">
         <v>38.04513743396946</v>
@@ -2192,34 +2224,34 @@
         <v>36</v>
       </c>
       <c r="AH8" t="n">
-        <v>217.8333333333333</v>
+        <v>217.3333333333333</v>
       </c>
       <c r="AI8" t="n">
-        <v>54.32888101746273</v>
+        <v>53.8730135848608</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.06409120815436428</v>
+        <v>0.06444407576172193</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.04665256891132195</v>
+        <v>0.04676133355126896</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AN8" t="n">
-        <v>281.8333333333333</v>
+        <v>281.6333333333333</v>
       </c>
       <c r="AO8" t="n">
-        <v>27.12449996492495</v>
+        <v>26.00857338600871</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.06776786954024958</v>
+        <v>0.06791361896658579</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.03670881239538504</v>
+        <v>0.03660716346371418</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2237,10 +2269,10 @@
         <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AX8" t="n">
-        <v>77.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="AY8" t="n">
         <v>10.5073568840869</v>
@@ -2273,10 +2305,10 @@
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BJ8" t="n">
-        <v>71.96666666666667</v>
+        <v>66.43333333333334</v>
       </c>
       <c r="BK8" t="n">
         <v>13.06169441627893</v>
@@ -2291,94 +2323,94 @@
         <v>0</v>
       </c>
       <c r="BO8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BP8" t="n">
         <v>95.3</v>
       </c>
       <c r="BQ8" t="n">
-        <v>44.0703907396046</v>
+        <v>21.61741609679784</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.05208034485172619</v>
+        <v>0.04645902831929943</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.0278058475248113</v>
+        <v>0.02368531483741892</v>
       </c>
       <c r="BT8" t="n">
         <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>10.09907685134871</v>
+        <v>3.121951844260493</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.05794280942223479</v>
+        <v>0.07753418788577242</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.03857962535670664</v>
+        <v>0.04403551212799017</v>
       </c>
       <c r="BX8" t="n">
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="BZ8" t="n">
-        <v>77.66666666666667</v>
+        <v>33.06666666666667</v>
       </c>
       <c r="CA8" t="n">
-        <v>13.57358195680669</v>
+        <v>4.909066877671674</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.05423968530639706</v>
+        <v>0.04843532998198223</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.03032919827816001</v>
+        <v>0.02590967214286791</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="CF8" t="n">
-        <v>160.8</v>
+        <v>78.26666666666667</v>
       </c>
       <c r="CG8" t="n">
-        <v>12.71906841438105</v>
+        <v>7.366904538343037</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.05027309168365043</v>
+        <v>0.04768245843098744</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.02906333571595467</v>
+        <v>0.02720873299113919</v>
       </c>
       <c r="CJ8" t="n">
         <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="CL8" t="n">
-        <v>90.23333333333333</v>
+        <v>44.23333333333333</v>
       </c>
       <c r="CM8" t="n">
-        <v>18.24655057615413</v>
+        <v>7.887026030459659</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.04645867549719697</v>
+        <v>0.04206824563838323</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.02858878767486099</v>
+        <v>0.02207006888061697</v>
       </c>
       <c r="CP8" t="n">
         <v>0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="CR8" t="n">
-        <v>273.9333333333333</v>
+        <v>144.4333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -2388,46 +2420,46 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67.8</v>
+        <v>119.4</v>
       </c>
       <c r="C9" t="n">
-        <v>29.33333333333333</v>
+        <v>48.03333333333333</v>
       </c>
       <c r="D9" t="n">
-        <v>40</v>
+        <v>71.8</v>
       </c>
       <c r="E9" t="n">
+        <v>21.06666666666667</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>11.96666666666667</v>
+      </c>
+      <c r="H9" t="n">
+        <v>31.23333333333333</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>11.73333333333333</v>
+      </c>
+      <c r="K9" t="n">
         <v>10.26666666666667</v>
       </c>
-      <c r="F9" t="n">
-        <v>4.533333333333333</v>
-      </c>
-      <c r="G9" t="n">
-        <v>6.966666666666667</v>
-      </c>
-      <c r="H9" t="n">
-        <v>39.03333333333333</v>
-      </c>
-      <c r="I9" t="n">
-        <v>6.933333333333334</v>
-      </c>
-      <c r="J9" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>9.6</v>
-      </c>
       <c r="L9" t="n">
-        <v>6.2</v>
+        <v>9.233333333333333</v>
       </c>
       <c r="M9" t="n">
-        <v>94.10398953578779</v>
+        <v>93.740513285533</v>
       </c>
       <c r="N9" t="n">
-        <v>0.07945469104207348</v>
+        <v>0.07993439558011151</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04485544328152835</v>
+        <v>0.04464093384439738</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -2445,10 +2477,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="V9" t="n">
-        <v>215.5</v>
+        <v>213.1</v>
       </c>
       <c r="W9" t="n">
         <v>52.88305594250869</v>
@@ -2469,22 +2501,22 @@
         <v>235.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>52.29390857152498</v>
+        <v>48.62639297113594</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0763849868001933</v>
+        <v>0.07589416447645971</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.04662450468894857</v>
+        <v>0.0458870620390237</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AH9" t="n">
-        <v>254.7</v>
+        <v>254.2333333333333</v>
       </c>
       <c r="AI9" t="n">
         <v>47.48671875942098</v>
@@ -2502,16 +2534,16 @@
         <v>61</v>
       </c>
       <c r="AN9" t="n">
-        <v>197.8</v>
+        <v>197.4333333333333</v>
       </c>
       <c r="AO9" t="n">
-        <v>25.77692077196959</v>
+        <v>25.37728434240364</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.06572247151153843</v>
+        <v>0.06603620027849147</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.03261536361861156</v>
+        <v>0.03252976903360738</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2529,10 +2561,10 @@
         <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX9" t="n">
-        <v>77.09999999999999</v>
+        <v>75.76666666666667</v>
       </c>
       <c r="AY9" t="n">
         <v>9.779698696765387</v>
@@ -2565,10 +2597,10 @@
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BJ9" t="n">
-        <v>67.83333333333333</v>
+        <v>64.86666666666666</v>
       </c>
       <c r="BK9" t="n">
         <v>10.9020853253041</v>
@@ -2589,88 +2621,88 @@
         <v>69.90000000000001</v>
       </c>
       <c r="BQ9" t="n">
-        <v>28.78562172180248</v>
+        <v>13.99083180686721</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.02855515230051864</v>
+        <v>0.02469264487425565</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.01103630888652402</v>
+        <v>0.008895973095103371</v>
       </c>
       <c r="BT9" t="n">
         <v>1.033333333333333</v>
       </c>
       <c r="BU9" t="n">
-        <v>13.85771872143386</v>
+        <v>6.390609757926585</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.0295192943909187</v>
+        <v>0.01720939321482704</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.01197875190199651</v>
+        <v>0.007755654886744216</v>
       </c>
       <c r="BX9" t="n">
         <v>1.033333333333333</v>
       </c>
       <c r="BY9" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="BZ9" t="n">
-        <v>209.8666666666667</v>
+        <v>136.7</v>
       </c>
       <c r="CA9" t="n">
-        <v>9.808737027910141</v>
+        <v>1.592374492131779</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.02890953338690899</v>
+        <v>0.05052576632712277</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.01371235671306201</v>
+        <v>0.02866482596669425</v>
       </c>
       <c r="CD9" t="n">
         <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="CF9" t="n">
-        <v>131.3333333333333</v>
+        <v>60.56666666666667</v>
       </c>
       <c r="CG9" t="n">
-        <v>6.979891061193634</v>
+        <v>2.136965805173824</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.04889218501119308</v>
+        <v>0.06153878617450574</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.02149185069885053</v>
+        <v>0.02715765593653472</v>
       </c>
       <c r="CJ9" t="n">
         <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="CL9" t="n">
-        <v>104.7333333333333</v>
+        <v>63.1</v>
       </c>
       <c r="CM9" t="n">
-        <v>10.5033707338922</v>
+        <v>5.894044846559037</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.03185087130479509</v>
+        <v>0.04536837635167443</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.01231909749795091</v>
+        <v>0.02095065115237264</v>
       </c>
       <c r="CP9" t="n">
         <v>0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="CR9" t="n">
-        <v>159.0333333333333</v>
+        <v>39.63333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -2680,46 +2712,46 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37.36666666666667</v>
+        <v>45.6</v>
       </c>
       <c r="C10" t="n">
-        <v>13.3</v>
+        <v>21.33333333333333</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>24.26666666666667</v>
       </c>
       <c r="E10" t="n">
-        <v>5.066666666666666</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="F10" t="n">
+        <v>3.933333333333333</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H10" t="n">
+        <v>16.46666666666667</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.266666666666667</v>
+      </c>
+      <c r="J10" t="n">
         <v>1.9</v>
       </c>
-      <c r="G10" t="n">
-        <v>1.433333333333333</v>
-      </c>
-      <c r="H10" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4.533333333333333</v>
-      </c>
       <c r="K10" t="n">
-        <v>6.266666666666667</v>
+        <v>7.3</v>
       </c>
       <c r="L10" t="n">
-        <v>4.366666666666666</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>60.54743723586119</v>
+        <v>59.79333743728606</v>
       </c>
       <c r="N10" t="n">
-        <v>0.03193341547054068</v>
+        <v>0.03157757305058467</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01714141070295111</v>
+        <v>0.01686312009763102</v>
       </c>
       <c r="P10" t="n">
         <v>4.233333333333333</v>
@@ -2794,16 +2826,16 @@
         <v>33</v>
       </c>
       <c r="AN10" t="n">
-        <v>406.0666666666667</v>
+        <v>393.7666666666667</v>
       </c>
       <c r="AO10" t="n">
-        <v>14.73326336640361</v>
+        <v>14.4727056103569</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.02809834634369368</v>
+        <v>0.02884067767302489</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.01603129961107466</v>
+        <v>0.01617520898457164</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2842,7 +2874,7 @@
         <v>11</v>
       </c>
       <c r="BD10" t="n">
-        <v>182.2333333333333</v>
+        <v>173.2333333333333</v>
       </c>
       <c r="BE10" t="n">
         <v>5.199159441613494</v>
@@ -2881,96 +2913,101 @@
         <v>39.73333333333333</v>
       </c>
       <c r="BQ10" t="n">
-        <v>28.62452369812576</v>
+        <v>13.41000502786665</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.02352494390303211</v>
+        <v>0.02260324779727702</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.01225158037495111</v>
+        <v>0.01098595456147922</v>
       </c>
       <c r="BT10" t="n">
-        <v>8.433333333333334</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="BU10" t="n">
-        <v>9.086350986549796</v>
+        <v>5.758069388702578</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.03136269670594966</v>
+        <v>0.02700607895013932</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.02049481153810138</v>
+        <v>0.01680373757530689</v>
       </c>
       <c r="BX10" t="n">
         <v>1.033333333333333</v>
       </c>
       <c r="BY10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BZ10" t="n">
-        <v>41.36666666666667</v>
+        <v>23.93333333333333</v>
       </c>
       <c r="CA10" t="n">
-        <v>13.47038403175038</v>
+        <v>0.5208267941665171</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.02495553813251972</v>
+        <v>0.05166280715712257</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.01293777968635052</v>
+        <v>0.03068980877239605</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.166666666666667</v>
+        <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CF10" t="n">
-        <v>87.43333333333334</v>
+        <v>27.7</v>
       </c>
       <c r="CG10" t="n">
-        <v>9.887047256022337</v>
+        <v>7.881210916661232</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.02310862701203688</v>
+        <v>0.02115159037274897</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.01080149101457332</v>
+        <v>0.009605032931323964</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.066666666666667</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="CL10" t="n">
-        <v>142.3</v>
+        <v>90.36666666666666</v>
       </c>
       <c r="CM10" t="n">
-        <v>16.28748031056705</v>
+        <v>2.564921858750531</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.02016412282887304</v>
+        <v>0.01625589524176313</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.01029825790653279</v>
+        <v>0.005817883835820825</v>
       </c>
       <c r="CP10" t="n">
-        <v>6.233333333333333</v>
+        <v>0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="CR10" t="n">
-        <v>364.2333333333333</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="B1:L1"/>
+  <mergeCells count="24">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:L1"/>
     <mergeCell ref="M1:AN1"/>
     <mergeCell ref="AO1:BP1"/>
     <mergeCell ref="BQ1:CR1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:L2"/>
     <mergeCell ref="M2:P2"/>
     <mergeCell ref="Q2:V2"/>
     <mergeCell ref="W2:AB2"/>
